--- a/data/trans_orig/Q02D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan</t>
+          <t>Número medio de horas diarias, a la semana, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,42</t>
+          <t>5,27; 7,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,19</t>
+          <t>5,04; 6,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 7,79</t>
+          <t>5,6; 7,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 11,12</t>
+          <t>4,4; 11,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,0</t>
+          <t>5,64; 7,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 6,93</t>
+          <t>5,98; 6,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,58</t>
+          <t>7,6; 9,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,33</t>
+          <t>5,22; 9,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 6,8</t>
+          <t>5,66; 6,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 6,56</t>
+          <t>5,84; 6,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 8,52</t>
+          <t>7,11; 8,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,9</t>
+          <t>5,34; 8,77</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,86</t>
+          <t>3,07; 3,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,15</t>
+          <t>4,55; 5,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 7,7</t>
+          <t>6,58; 7,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,98</t>
+          <t>4,92; 6,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 6,84</t>
+          <t>5,83; 6,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,1</t>
+          <t>6,6; 7,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 9,45</t>
+          <t>8,48; 9,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 8,81</t>
+          <t>7,27; 8,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,52</t>
+          <t>4,81; 5,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 6,23</t>
+          <t>5,81; 6,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,87; 8,6</t>
+          <t>7,89; 8,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,73</t>
+          <t>6,55; 7,73</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,42</t>
+          <t>3,08; 4,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,04</t>
+          <t>4,07; 5,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 7,21</t>
+          <t>5,71; 7,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 11,03</t>
+          <t>6,38; 10,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,56</t>
+          <t>5,06; 6,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 7,45</t>
+          <t>6,39; 7,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,57; 10,32</t>
+          <t>8,58; 10,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,09</t>
+          <t>7,66; 10,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,43</t>
+          <t>4,33; 5,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,27</t>
+          <t>5,48; 6,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 8,86</t>
+          <t>7,62; 8,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,74</t>
+          <t>7,44; 9,86</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 4,33</t>
+          <t>3,65; 4,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 5,16</t>
+          <t>4,68; 5,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,35</t>
+          <t>6,53; 7,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,34</t>
+          <t>5,48; 7,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 6,55</t>
+          <t>5,87; 6,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,97</t>
+          <t>6,55; 6,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 9,34</t>
+          <t>8,61; 9,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,58</t>
+          <t>7,41; 8,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,19</t>
+          <t>5,87; 6,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 8,44</t>
+          <t>7,83; 8,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,94</t>
+          <t>6,82; 7,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q02D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_R-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>6,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>6,85</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 7,46</t>
+          <t>5,22; 7,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,17</t>
+          <t>5,04; 6,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 7,8</t>
+          <t>5,65; 7,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,02</t>
+          <t>4,59; 9,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,03</t>
+          <t>5,62; 7,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 6,9</t>
+          <t>5,99; 6,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 9,58</t>
+          <t>7,61; 9,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,23</t>
+          <t>5,72; 9,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 6,81</t>
+          <t>5,7; 6,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 6,56</t>
+          <t>5,83; 6,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,52</t>
+          <t>7,04; 8,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,77</t>
+          <t>5,65; 8,33</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,07</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,88</t>
+          <t>3,09; 3,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,12</t>
+          <t>4,56; 5,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 7,65</t>
+          <t>6,59; 7,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,81</t>
+          <t>4,94; 6,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 6,79</t>
+          <t>5,85; 6,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,12</t>
+          <t>6,6; 7,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 9,43</t>
+          <t>8,5; 9,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 8,77</t>
+          <t>7,29; 8,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,49</t>
+          <t>4,77; 5,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 6,25</t>
+          <t>5,82; 6,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 8,59</t>
+          <t>7,85; 8,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 7,73</t>
+          <t>6,57; 7,66</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>8,43</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,43</t>
+          <t>8,13</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,43</t>
+          <t>3,1; 4,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 5,02</t>
+          <t>4,08; 5,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 7,2</t>
+          <t>5,82; 7,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,86</t>
+          <t>6,2; 10,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 6,66</t>
+          <t>5,04; 6,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 7,51</t>
+          <t>6,32; 7,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,28</t>
+          <t>8,57; 10,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,14</t>
+          <t>7,36; 9,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 5,51</t>
+          <t>4,35; 5,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,31</t>
+          <t>5,5; 6,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 8,81</t>
+          <t>7,67; 8,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 9,86</t>
+          <t>7,23; 9,37</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,96</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,34</t>
+          <t>3,65; 4,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,16</t>
+          <t>4,69; 5,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,4</t>
+          <t>6,5; 7,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,29</t>
+          <t>5,45; 7,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,55</t>
+          <t>5,85; 6,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,55; 6,98</t>
+          <t>6,57; 6,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 9,35</t>
+          <t>8,56; 9,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,69</t>
+          <t>7,42; 8,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 5,64</t>
+          <t>5,08; 5,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,18</t>
+          <t>5,87; 6,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 8,41</t>
+          <t>7,83; 8,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,84</t>
+          <t>6,78; 7,74</t>
         </is>
       </c>
     </row>
